--- a/inputs/historico_conectividad.xlsx
+++ b/inputs/historico_conectividad.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupokaufmann-my.sharepoint.com/personal/samuel_sanchez_grupokaufmann_com/Documents/Documentos/Dev/QS/outQS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupokaufmann-my.sharepoint.com/personal/samuel_sanchez_grupokaufmann_com/Documents/Documentos/Dev/QS/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_89468FE75A0C99E0C7DCAC553DB552D7BCEF3D85" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A25CFFA-C871-4E03-9DF3-C8D039346E26}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_284303FFDB052CF58DDDAB5ECE1BE559F2286E9C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E59354F4-3603-403F-929C-D6E0AD4F4CA0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="16">
   <si>
     <t>fecha</t>
   </si>
@@ -148,10 +148,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -439,22 +435,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
@@ -1725,744 +1709,6 @@
         <v>3.46</v>
       </c>
       <c r="M31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A32" s="2">
-        <v>45957</v>
-      </c>
-      <c r="B32" t="s">
-        <v>13</v>
-      </c>
-      <c r="C32">
-        <v>5879</v>
-      </c>
-      <c r="D32">
-        <v>3424</v>
-      </c>
-      <c r="E32">
-        <v>662</v>
-      </c>
-      <c r="F32">
-        <v>268</v>
-      </c>
-      <c r="G32">
-        <v>508</v>
-      </c>
-      <c r="H32">
-        <v>1017</v>
-      </c>
-      <c r="I32">
-        <v>58.24</v>
-      </c>
-      <c r="J32">
-        <v>11.26</v>
-      </c>
-      <c r="K32">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="L32">
-        <v>8.64</v>
-      </c>
-      <c r="M32">
-        <v>17.3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A33" s="2">
-        <v>45957</v>
-      </c>
-      <c r="B33" t="s">
-        <v>14</v>
-      </c>
-      <c r="C33">
-        <v>5273</v>
-      </c>
-      <c r="D33">
-        <v>4648</v>
-      </c>
-      <c r="E33">
-        <v>359</v>
-      </c>
-      <c r="F33">
-        <v>140</v>
-      </c>
-      <c r="G33">
-        <v>122</v>
-      </c>
-      <c r="H33">
-        <v>4</v>
-      </c>
-      <c r="I33">
-        <v>88.15</v>
-      </c>
-      <c r="J33">
-        <v>6.81</v>
-      </c>
-      <c r="K33">
-        <v>2.66</v>
-      </c>
-      <c r="L33">
-        <v>2.31</v>
-      </c>
-      <c r="M33">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A34" s="2">
-        <v>45957</v>
-      </c>
-      <c r="B34" t="s">
-        <v>15</v>
-      </c>
-      <c r="C34">
-        <v>11144</v>
-      </c>
-      <c r="D34">
-        <v>9447</v>
-      </c>
-      <c r="E34">
-        <v>910</v>
-      </c>
-      <c r="F34">
-        <v>373</v>
-      </c>
-      <c r="G34">
-        <v>414</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-      <c r="I34">
-        <v>84.77</v>
-      </c>
-      <c r="J34">
-        <v>8.17</v>
-      </c>
-      <c r="K34">
-        <v>3.35</v>
-      </c>
-      <c r="L34">
-        <v>3.72</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A35" s="2">
-        <v>45958</v>
-      </c>
-      <c r="B35" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35">
-        <v>5874</v>
-      </c>
-      <c r="D35">
-        <v>3492</v>
-      </c>
-      <c r="E35">
-        <v>587</v>
-      </c>
-      <c r="F35">
-        <v>279</v>
-      </c>
-      <c r="G35">
-        <v>507</v>
-      </c>
-      <c r="H35">
-        <v>1009</v>
-      </c>
-      <c r="I35">
-        <v>59.45</v>
-      </c>
-      <c r="J35">
-        <v>9.99</v>
-      </c>
-      <c r="K35">
-        <v>4.75</v>
-      </c>
-      <c r="L35">
-        <v>8.6300000000000008</v>
-      </c>
-      <c r="M35">
-        <v>17.18</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A36" s="2">
-        <v>45958</v>
-      </c>
-      <c r="B36" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36">
-        <v>5206</v>
-      </c>
-      <c r="D36">
-        <v>4591</v>
-      </c>
-      <c r="E36">
-        <v>348</v>
-      </c>
-      <c r="F36">
-        <v>148</v>
-      </c>
-      <c r="G36">
-        <v>118</v>
-      </c>
-      <c r="H36">
-        <v>1</v>
-      </c>
-      <c r="I36">
-        <v>88.19</v>
-      </c>
-      <c r="J36">
-        <v>6.68</v>
-      </c>
-      <c r="K36">
-        <v>2.84</v>
-      </c>
-      <c r="L36">
-        <v>2.27</v>
-      </c>
-      <c r="M36">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A37" s="2">
-        <v>45958</v>
-      </c>
-      <c r="B37" t="s">
-        <v>15</v>
-      </c>
-      <c r="C37">
-        <v>11078</v>
-      </c>
-      <c r="D37">
-        <v>9437</v>
-      </c>
-      <c r="E37">
-        <v>840</v>
-      </c>
-      <c r="F37">
-        <v>390</v>
-      </c>
-      <c r="G37">
-        <v>411</v>
-      </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-      <c r="I37">
-        <v>85.19</v>
-      </c>
-      <c r="J37">
-        <v>7.58</v>
-      </c>
-      <c r="K37">
-        <v>3.52</v>
-      </c>
-      <c r="L37">
-        <v>3.71</v>
-      </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A38" s="2">
-        <v>45959</v>
-      </c>
-      <c r="B38" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38">
-        <v>5874</v>
-      </c>
-      <c r="D38">
-        <v>3559</v>
-      </c>
-      <c r="E38">
-        <v>498</v>
-      </c>
-      <c r="F38">
-        <v>286</v>
-      </c>
-      <c r="G38">
-        <v>512</v>
-      </c>
-      <c r="H38">
-        <v>1019</v>
-      </c>
-      <c r="I38">
-        <v>60.59</v>
-      </c>
-      <c r="J38">
-        <v>8.48</v>
-      </c>
-      <c r="K38">
-        <v>4.87</v>
-      </c>
-      <c r="L38">
-        <v>8.7200000000000006</v>
-      </c>
-      <c r="M38">
-        <v>17.350000000000001</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A39" s="2">
-        <v>45959</v>
-      </c>
-      <c r="B39" t="s">
-        <v>14</v>
-      </c>
-      <c r="C39">
-        <v>5206</v>
-      </c>
-      <c r="D39">
-        <v>4609</v>
-      </c>
-      <c r="E39">
-        <v>323</v>
-      </c>
-      <c r="F39">
-        <v>157</v>
-      </c>
-      <c r="G39">
-        <v>116</v>
-      </c>
-      <c r="H39">
-        <v>1</v>
-      </c>
-      <c r="I39">
-        <v>88.53</v>
-      </c>
-      <c r="J39">
-        <v>6.2</v>
-      </c>
-      <c r="K39">
-        <v>3.02</v>
-      </c>
-      <c r="L39">
-        <v>2.23</v>
-      </c>
-      <c r="M39">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A40" s="2">
-        <v>45959</v>
-      </c>
-      <c r="B40" t="s">
-        <v>15</v>
-      </c>
-      <c r="C40">
-        <v>11078</v>
-      </c>
-      <c r="D40">
-        <v>9491</v>
-      </c>
-      <c r="E40">
-        <v>760</v>
-      </c>
-      <c r="F40">
-        <v>414</v>
-      </c>
-      <c r="G40">
-        <v>413</v>
-      </c>
-      <c r="H40">
-        <v>0</v>
-      </c>
-      <c r="I40">
-        <v>85.67</v>
-      </c>
-      <c r="J40">
-        <v>6.86</v>
-      </c>
-      <c r="K40">
-        <v>3.74</v>
-      </c>
-      <c r="L40">
-        <v>3.73</v>
-      </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A41" s="2">
-        <v>45985</v>
-      </c>
-      <c r="B41" t="s">
-        <v>13</v>
-      </c>
-      <c r="C41">
-        <v>5894</v>
-      </c>
-      <c r="D41">
-        <v>3413</v>
-      </c>
-      <c r="E41">
-        <v>645</v>
-      </c>
-      <c r="F41">
-        <v>156</v>
-      </c>
-      <c r="G41">
-        <v>680</v>
-      </c>
-      <c r="H41">
-        <v>1000</v>
-      </c>
-      <c r="I41">
-        <v>57.91</v>
-      </c>
-      <c r="J41">
-        <v>10.94</v>
-      </c>
-      <c r="K41">
-        <v>2.65</v>
-      </c>
-      <c r="L41">
-        <v>11.54</v>
-      </c>
-      <c r="M41">
-        <v>16.97</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A42" s="2">
-        <v>45985</v>
-      </c>
-      <c r="B42" t="s">
-        <v>14</v>
-      </c>
-      <c r="C42">
-        <v>5301</v>
-      </c>
-      <c r="D42">
-        <v>4606</v>
-      </c>
-      <c r="E42">
-        <v>412</v>
-      </c>
-      <c r="F42">
-        <v>92</v>
-      </c>
-      <c r="G42">
-        <v>185</v>
-      </c>
-      <c r="H42">
-        <v>6</v>
-      </c>
-      <c r="I42">
-        <v>86.89</v>
-      </c>
-      <c r="J42">
-        <v>7.77</v>
-      </c>
-      <c r="K42">
-        <v>1.74</v>
-      </c>
-      <c r="L42">
-        <v>3.49</v>
-      </c>
-      <c r="M42">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A43" s="2">
-        <v>45985</v>
-      </c>
-      <c r="B43" t="s">
-        <v>15</v>
-      </c>
-      <c r="C43">
-        <v>11189</v>
-      </c>
-      <c r="D43">
-        <v>9362</v>
-      </c>
-      <c r="E43">
-        <v>978</v>
-      </c>
-      <c r="F43">
-        <v>232</v>
-      </c>
-      <c r="G43">
-        <v>617</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <v>83.67</v>
-      </c>
-      <c r="J43">
-        <v>8.74</v>
-      </c>
-      <c r="K43">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="L43">
-        <v>5.51</v>
-      </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A44" s="2">
-        <v>45986</v>
-      </c>
-      <c r="B44" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44">
-        <v>5898</v>
-      </c>
-      <c r="D44">
-        <v>3455</v>
-      </c>
-      <c r="E44">
-        <v>580</v>
-      </c>
-      <c r="F44">
-        <v>166</v>
-      </c>
-      <c r="G44">
-        <v>688</v>
-      </c>
-      <c r="H44">
-        <v>1009</v>
-      </c>
-      <c r="I44">
-        <v>58.58</v>
-      </c>
-      <c r="J44">
-        <v>9.83</v>
-      </c>
-      <c r="K44">
-        <v>2.81</v>
-      </c>
-      <c r="L44">
-        <v>11.66</v>
-      </c>
-      <c r="M44">
-        <v>17.11</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A45" s="2">
-        <v>45986</v>
-      </c>
-      <c r="B45" t="s">
-        <v>14</v>
-      </c>
-      <c r="C45">
-        <v>5305</v>
-      </c>
-      <c r="D45">
-        <v>4636</v>
-      </c>
-      <c r="E45">
-        <v>385</v>
-      </c>
-      <c r="F45">
-        <v>94</v>
-      </c>
-      <c r="G45">
-        <v>184</v>
-      </c>
-      <c r="H45">
-        <v>6</v>
-      </c>
-      <c r="I45">
-        <v>87.39</v>
-      </c>
-      <c r="J45">
-        <v>7.26</v>
-      </c>
-      <c r="K45">
-        <v>1.77</v>
-      </c>
-      <c r="L45">
-        <v>3.47</v>
-      </c>
-      <c r="M45">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A46" s="2">
-        <v>45986</v>
-      </c>
-      <c r="B46" t="s">
-        <v>15</v>
-      </c>
-      <c r="C46">
-        <v>11197</v>
-      </c>
-      <c r="D46">
-        <v>9419</v>
-      </c>
-      <c r="E46">
-        <v>922</v>
-      </c>
-      <c r="F46">
-        <v>244</v>
-      </c>
-      <c r="G46">
-        <v>612</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>84.12</v>
-      </c>
-      <c r="J46">
-        <v>8.23</v>
-      </c>
-      <c r="K46">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="L46">
-        <v>5.47</v>
-      </c>
-      <c r="M46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A47" s="2">
-        <v>45992</v>
-      </c>
-      <c r="B47" t="s">
-        <v>13</v>
-      </c>
-      <c r="C47">
-        <v>5902</v>
-      </c>
-      <c r="D47">
-        <v>3305</v>
-      </c>
-      <c r="E47">
-        <v>729</v>
-      </c>
-      <c r="F47">
-        <v>183</v>
-      </c>
-      <c r="G47">
-        <v>678</v>
-      </c>
-      <c r="H47">
-        <v>1007</v>
-      </c>
-      <c r="I47">
-        <v>56</v>
-      </c>
-      <c r="J47">
-        <v>12.35</v>
-      </c>
-      <c r="K47">
-        <v>3.1</v>
-      </c>
-      <c r="L47">
-        <v>11.49</v>
-      </c>
-      <c r="M47">
-        <v>17.059999999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A48" s="2">
-        <v>45992</v>
-      </c>
-      <c r="B48" t="s">
-        <v>14</v>
-      </c>
-      <c r="C48">
-        <v>5299</v>
-      </c>
-      <c r="D48">
-        <v>4599</v>
-      </c>
-      <c r="E48">
-        <v>427</v>
-      </c>
-      <c r="F48">
-        <v>89</v>
-      </c>
-      <c r="G48">
-        <v>178</v>
-      </c>
-      <c r="H48">
-        <v>6</v>
-      </c>
-      <c r="I48">
-        <v>86.79</v>
-      </c>
-      <c r="J48">
-        <v>8.06</v>
-      </c>
-      <c r="K48">
-        <v>1.68</v>
-      </c>
-      <c r="L48">
-        <v>3.36</v>
-      </c>
-      <c r="M48">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A49" s="2">
-        <v>45992</v>
-      </c>
-      <c r="B49" t="s">
-        <v>15</v>
-      </c>
-      <c r="C49">
-        <v>11195</v>
-      </c>
-      <c r="D49">
-        <v>9275</v>
-      </c>
-      <c r="E49">
-        <v>1048</v>
-      </c>
-      <c r="F49">
-        <v>283</v>
-      </c>
-      <c r="G49">
-        <v>589</v>
-      </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49">
-        <v>82.85</v>
-      </c>
-      <c r="J49">
-        <v>9.36</v>
-      </c>
-      <c r="K49">
-        <v>2.5299999999999998</v>
-      </c>
-      <c r="L49">
-        <v>5.26</v>
-      </c>
-      <c r="M49">
         <v>0</v>
       </c>
     </row>
@@ -2475,9 +1721,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -2522,122 +1765,122 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
-        <v>45992</v>
+        <v>45954</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
       </c>
       <c r="C2">
-        <v>5902</v>
+        <v>5877</v>
       </c>
       <c r="D2">
-        <v>3305</v>
+        <v>3583</v>
       </c>
       <c r="E2">
-        <v>729</v>
+        <v>507</v>
       </c>
       <c r="F2">
-        <v>183</v>
+        <v>272</v>
       </c>
       <c r="G2">
-        <v>678</v>
+        <v>496</v>
       </c>
       <c r="H2">
-        <v>1007</v>
+        <v>1019</v>
       </c>
       <c r="I2">
-        <v>56</v>
+        <v>60.97</v>
       </c>
       <c r="J2">
-        <v>12.35</v>
+        <v>8.6300000000000008</v>
       </c>
       <c r="K2">
-        <v>3.1</v>
+        <v>4.63</v>
       </c>
       <c r="L2">
-        <v>11.49</v>
+        <v>8.44</v>
       </c>
       <c r="M2">
-        <v>17.059999999999999</v>
+        <v>17.34</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>45992</v>
+        <v>45954</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3">
-        <v>5299</v>
+        <v>5263</v>
       </c>
       <c r="D3">
-        <v>4599</v>
+        <v>4657</v>
       </c>
       <c r="E3">
-        <v>427</v>
+        <v>350</v>
       </c>
       <c r="F3">
-        <v>89</v>
+        <v>143</v>
       </c>
       <c r="G3">
-        <v>178</v>
+        <v>111</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>86.79</v>
+        <v>88.49</v>
       </c>
       <c r="J3">
-        <v>8.06</v>
+        <v>6.65</v>
       </c>
       <c r="K3">
-        <v>1.68</v>
+        <v>2.72</v>
       </c>
       <c r="L3">
-        <v>3.36</v>
+        <v>2.11</v>
       </c>
       <c r="M3">
-        <v>0.11</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
-        <v>45992</v>
+        <v>45954</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4">
-        <v>11195</v>
+        <v>11138</v>
       </c>
       <c r="D4">
-        <v>9275</v>
+        <v>9562</v>
       </c>
       <c r="E4">
-        <v>1048</v>
+        <v>798</v>
       </c>
       <c r="F4">
-        <v>283</v>
+        <v>393</v>
       </c>
       <c r="G4">
-        <v>589</v>
+        <v>385</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>82.85</v>
+        <v>85.85</v>
       </c>
       <c r="J4">
-        <v>9.36</v>
+        <v>7.16</v>
       </c>
       <c r="K4">
-        <v>2.5299999999999998</v>
+        <v>3.53</v>
       </c>
       <c r="L4">
-        <v>5.26</v>
+        <v>3.46</v>
       </c>
       <c r="M4">
         <v>0</v>
